--- a/1394_Cuenca_Tumbes/_raw_reportes_xlsx/IDConfig_64932_completo.xlsx
+++ b/1394_Cuenca_Tumbes/_raw_reportes_xlsx/IDConfig_64932_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R3617d582d70740af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R5fcceb8ebd6f4810"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.1720</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.1170</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.6437</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.6012</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.8394</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.8112</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.6892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.9216</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.8662</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/1394_Cuenca_Tumbes/_raw_reportes_xlsx/IDConfig_64932_completo.xlsx
+++ b/1394_Cuenca_Tumbes/_raw_reportes_xlsx/IDConfig_64932_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R5fcceb8ebd6f4810"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R2a9099a7c7054882"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     40.3193</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     58.0991</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     33.1393</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     32.2847</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     32.2589</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     36.3324</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     42.6593</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     37.1980</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     40.7214</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     44.6890</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     42.6882</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     43.4144</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     69.0343</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    207.0397</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     55.1920</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.1513</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     65.2168</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.2655</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.5862</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.4443</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.9852</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.4178</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.7400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.6126</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.9359</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.5353</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.3742</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.0426</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.1408</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.2983</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.0426</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.4530</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.4534</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.8958</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.4222</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.9432</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.8449</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.1941</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.5244</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.0848</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.3541</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.7903</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.4460</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.8460</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.3820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.3008</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.3016</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.9802</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.1720</x:v>
+        <x:v>     25.5162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +1014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.6437</x:v>
+        <x:v>     27.3166</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +1044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     29.8394</x:v>
+        <x:v>     31.2889</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +1059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     29.8112</x:v>
+        <x:v>     29.1020</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -399,7 +1119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     27.1483</x:v>
+        <x:v>     27.4873</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -429,7 +1149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     27.8008</x:v>
+        <x:v>     28.1446</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -579,7 +1299,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     30.7122</x:v>
+        <x:v>     30.3499</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2979,7 +3699,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>   1079.5738</x:v>
+        <x:v>   1075.9196</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3174,7 +3894,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    198.0179</x:v>
+        <x:v>    195.1946</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3264,7 +3984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    210.3251</x:v>
+        <x:v>    214.8137</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3369,7 +4089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    187.3929</x:v>
+        <x:v>    189.7528</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3459,7 +4179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    104.4254</x:v>
+        <x:v>    105.2533</x:v>
       </x:c>
     </x:row>
     <x:row>
